--- a/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>66.63013824272224</v>
+        <v>81.01576402177247</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>83.24518221853894</v>
+        <v>84.499937518341</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>99.66193933569537</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>108.80678833518</v>
+        <v>89.86020443613874</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.4752701701724</v>
+        <v>91.46828451147806</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>79.09245631047411</v>
+        <v>77.86463479154189</v>
       </c>
     </row>
     <row r="19">

--- a/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
@@ -2955,20 +2955,20 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue  (17.0% / 18.5% / 19.9% / 21.5% / 23.0%)</t>
+          <t>Working capital / revenue  (17.0% / 18.5% / 19.7% / 21.5% / 23.0%)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
         <v>97.75178736220548</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>92.24096877403932</v>
+        <v>92.24096877403929</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>87.09753809175092</v>
+        <v>87.94253027526975</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>81.21933159770705</v>
+        <v>81.21933159770703</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>75.70851300954091</v>

--- a/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
@@ -4030,14 +4030,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>28.56691644232448</v>
+        <v>46.85427404968456</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>138.175135007335</v>
+        <v>133.8340856637828</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>28.56691644232448</v>
+        <v>46.85427404968456</v>
       </c>
     </row>
     <row r="7">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>138.175135007335</v>
+        <v>133.8340856637828</v>
       </c>
     </row>
     <row r="8">

--- a/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_13092026_public.xlsx
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>176.1268087989355</v>
+        <v>154.4122355807261</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>129.2598114113915</v>
+        <v>113.259599566395</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>222.9938061864796</v>
+        <v>195.5648715950571</v>
       </c>
     </row>
     <row r="24">
@@ -4649,13 +4649,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>97.71822108324348</v>
+        <v>85.56378676759184</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>69.84198537113525</v>
+        <v>61.08642219003997</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>160.9699206371431</v>
+        <v>141.1033842268746</v>
       </c>
     </row>
     <row r="25">
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>89.4341891885301</v>
+        <v>78.28980361746039</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>66.70493817011291</v>
+        <v>58.33186634435741</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>112.1634402069473</v>
+        <v>98.24774089056336</v>
       </c>
     </row>
     <row r="26">
